--- a/artfynd/A 51680-2024 artfynd.xlsx
+++ b/artfynd/A 51680-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89161963</v>
+        <v>89161838</v>
       </c>
       <c r="B2" t="n">
-        <v>101325</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222056</v>
+        <v>100038</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor häxört</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Circaea lutetiana</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Blentarp bergtäkt, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411553.7188574545</v>
+        <v>411640</v>
       </c>
       <c r="R2" t="n">
-        <v>6155332.935619446</v>
+        <v>6155326</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -730,7 +729,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Skurup</t>
+          <t>Sjöbo</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -740,7 +739,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Slimminge</t>
+          <t>Blentarp</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -748,19 +747,9 @@
           <t>2020-07-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-07-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89161848</v>
+        <v>89161835</v>
       </c>
       <c r="B3" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223246</v>
+        <v>220075</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411718.0898120501</v>
+        <v>411615</v>
       </c>
       <c r="R3" t="n">
-        <v>6155271.900931061</v>
+        <v>6155306</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-06-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-06-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,32 +873,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89161833</v>
+        <v>89161884</v>
       </c>
       <c r="B4" t="n">
-        <v>101325</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222056</v>
+        <v>220075</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor häxört</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Circaea lutetiana</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -939,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411655.1212696324</v>
+        <v>411547</v>
       </c>
       <c r="R4" t="n">
-        <v>6155299.200843473</v>
+        <v>6155264</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-07-31</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-07-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,32 +970,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89161885</v>
+        <v>89161892</v>
       </c>
       <c r="B5" t="n">
-        <v>107952</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221049</v>
+        <v>220075</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Valeriana dioica</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1044,33 +998,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blentarp bergtäkt, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>411550.0249930859</v>
+        <v>411524</v>
       </c>
       <c r="R5" t="n">
-        <v>6155262.271849452</v>
+        <v>6155248</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,35 +1038,19 @@
           <t>2020-10-06</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-10-06</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Alsumpskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1145,32 +1067,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89161929</v>
+        <v>89161894</v>
       </c>
       <c r="B6" t="n">
-        <v>101325</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222056</v>
+        <v>220075</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor häxört</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Circaea lutetiana</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1185,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>411551.0939485605</v>
+        <v>411537</v>
       </c>
       <c r="R6" t="n">
-        <v>6155287.150291222</v>
+        <v>6155259</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,19 +1135,9 @@
           <t>2020-10-06</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,37 +1164,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89161921</v>
+        <v>89161922</v>
       </c>
       <c r="B7" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223246</v>
+        <v>220075</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1297,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>411548.0768864048</v>
+        <v>411555</v>
       </c>
       <c r="R7" t="n">
-        <v>6155278.156618836</v>
+        <v>6155268</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,19 +1232,9 @@
           <t>2020-10-06</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,32 +1261,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89161927</v>
+        <v>89161930</v>
       </c>
       <c r="B8" t="n">
-        <v>101325</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222056</v>
+        <v>220075</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor häxört</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Circaea lutetiana</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1409,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411529.7572497749</v>
+        <v>411548</v>
       </c>
       <c r="R8" t="n">
-        <v>6155297.767052596</v>
+        <v>6155284</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,19 +1329,9 @@
           <t>2020-10-06</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,32 +1358,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89161879</v>
+        <v>89161932</v>
       </c>
       <c r="B9" t="n">
-        <v>101325</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222056</v>
+        <v>220075</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor häxört</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Circaea lutetiana</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1521,10 +1393,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411618.7600781045</v>
+        <v>411521</v>
       </c>
       <c r="R9" t="n">
-        <v>6155295.972237438</v>
+        <v>6155265</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,22 +1423,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-06-02</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-06-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,37 +1455,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89161877</v>
+        <v>89161934</v>
       </c>
       <c r="B10" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223246</v>
+        <v>220075</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1633,10 +1490,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>411670.0058654235</v>
+        <v>411522</v>
       </c>
       <c r="R10" t="n">
-        <v>6155277.962436859</v>
+        <v>6155274</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,22 +1520,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-06-02</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-06-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,32 +1552,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89161849</v>
+        <v>89161923</v>
       </c>
       <c r="B11" t="n">
-        <v>101325</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222056</v>
+        <v>220785</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor häxört</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Circaea lutetiana</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1745,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>411682.2411599918</v>
+        <v>411579</v>
       </c>
       <c r="R11" t="n">
-        <v>6155294.127287745</v>
+        <v>6155244</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,22 +1617,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-06-02</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-06-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,37 +1649,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89161928</v>
+        <v>89161925</v>
       </c>
       <c r="B12" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223246</v>
+        <v>220785</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1857,10 +1684,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>411550.2796442129</v>
+        <v>411580</v>
       </c>
       <c r="R12" t="n">
-        <v>6155303.012100409</v>
+        <v>6155227</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1890,19 +1717,9 @@
           <t>2020-10-06</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,50 +1746,61 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89161878</v>
+        <v>89161885</v>
       </c>
       <c r="B13" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111129</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223246</v>
+        <v>221049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Valeriana dioica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Blentarp bergtäkt, Sk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>411660.9582685984</v>
+        <v>411550</v>
       </c>
       <c r="R13" t="n">
-        <v>6155279.276515638</v>
+        <v>6155262</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1999,22 +1827,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2020-06-02</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2020-06-02</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,8 +1841,14 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2041,15 +1865,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89161957</v>
+        <v>89161833</v>
       </c>
       <c r="B14" t="n">
-        <v>101325</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104255</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,10 +1900,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>411568.2184884017</v>
+        <v>411655</v>
       </c>
       <c r="R14" t="n">
-        <v>6155320.759224823</v>
+        <v>6155299</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2114,19 +1933,9 @@
           <t>2020-07-31</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2020-07-31</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,6 +1959,1655 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>89161840</v>
+      </c>
+      <c r="B15" t="n">
+        <v>104255</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222056</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Stor häxört</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Circaea lutetiana</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Blentarp bergtäkt, Sk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>411702</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6155316</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sjöbo</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Blentarp</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2020-07-31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2020-07-31</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>89161849</v>
+      </c>
+      <c r="B16" t="n">
+        <v>104255</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222056</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Stor häxört</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Circaea lutetiana</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Blentarp bergtäkt, Sk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>411682</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6155294</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skurup</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Slimminge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2020-06-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2020-06-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>89161879</v>
+      </c>
+      <c r="B17" t="n">
+        <v>104255</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222056</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Stor häxört</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Circaea lutetiana</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Blentarp bergtäkt, Sk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>411619</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6155296</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skurup</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Slimminge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2020-06-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2020-06-02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>89161886</v>
+      </c>
+      <c r="B18" t="n">
+        <v>104255</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222056</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Stor häxört</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Circaea lutetiana</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Blentarp bergtäkt, Sk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>411554</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6155242</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skurup</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Slimminge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>89161927</v>
+      </c>
+      <c r="B19" t="n">
+        <v>104255</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222056</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Stor häxört</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Circaea lutetiana</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Blentarp bergtäkt, Sk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>411530</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6155298</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skurup</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Slimminge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>89161929</v>
+      </c>
+      <c r="B20" t="n">
+        <v>104255</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222056</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Stor häxört</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Circaea lutetiana</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Blentarp bergtäkt, Sk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>411551</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6155287</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skurup</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Slimminge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>89161931</v>
+      </c>
+      <c r="B21" t="n">
+        <v>104255</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222056</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Stor häxört</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Circaea lutetiana</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Blentarp bergtäkt, Sk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>411517</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6155255</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skurup</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Slimminge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>89161957</v>
+      </c>
+      <c r="B22" t="n">
+        <v>104255</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222056</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Stor häxört</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Circaea lutetiana</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Blentarp bergtäkt, Sk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>411568</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6155321</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skurup</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Slimminge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2020-07-31</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2020-07-31</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>89161963</v>
+      </c>
+      <c r="B23" t="n">
+        <v>104255</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222056</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Stor häxört</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Circaea lutetiana</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Blentarp bergtäkt, Sk</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>411554</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6155333</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Skurup</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Slimminge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2020-07-31</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2020-07-31</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>89161848</v>
+      </c>
+      <c r="B24" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Blentarp bergtäkt, Sk</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>411718</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6155272</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skurup</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Slimminge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2020-06-02</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2020-06-02</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>89161875</v>
+      </c>
+      <c r="B25" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Blentarp bergtäkt, Sk</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>411535</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6155330</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skurup</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Slimminge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2020-06-02</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2020-06-02</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>89161877</v>
+      </c>
+      <c r="B26" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Blentarp bergtäkt, Sk</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>411670</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6155278</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skurup</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Slimminge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2020-06-02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2020-06-02</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>89161878</v>
+      </c>
+      <c r="B27" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Blentarp bergtäkt, Sk</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>411661</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6155279</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skurup</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Slimminge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2020-06-02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2020-06-02</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>89161921</v>
+      </c>
+      <c r="B28" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Blentarp bergtäkt, Sk</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>411548</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6155278</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skurup</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Slimminge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>89161924</v>
+      </c>
+      <c r="B29" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Blentarp bergtäkt, Sk</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>411580</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6155227</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Skurup</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Slimminge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>89161928</v>
+      </c>
+      <c r="B30" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Blentarp bergtäkt, Sk</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>411550</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6155303</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Skurup</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Slimminge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>89161933</v>
+      </c>
+      <c r="B31" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Blentarp bergtäkt, Sk</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>411521</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6155265</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Skurup</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Slimminge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51680-2024 artfynd.xlsx
+++ b/artfynd/A 51680-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161838</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161835</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161884</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161892</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161894</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161922</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161930</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161932</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161934</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161923</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161925</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1862,6 +1922,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161885</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1959,6 +2024,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161833</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2056,6 +2126,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161840</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2153,6 +2228,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161849</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2250,6 +2330,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161879</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2347,6 +2432,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161886</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2444,6 +2534,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161927</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2541,6 +2636,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161929</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2638,6 +2738,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161931</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2735,6 +2840,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161957</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2832,6 +2942,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161963</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2929,6 +3044,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161848</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3026,6 +3146,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161875</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3123,6 +3248,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161877</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3220,6 +3350,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161878</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3317,6 +3452,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161921</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3414,6 +3554,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161924</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3511,6 +3656,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161928</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3608,8 +3758,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89161933</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>